--- a/outputs/AI Inference Economics.xlsx
+++ b/outputs/AI Inference Economics.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Whole market (OpenRouter)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segment summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GPU prices" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sensitivity" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Whole market (OpenRouter)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Segment summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GPU prices" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="API prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Benchmarks" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/AI Inference Economics.xlsx
+++ b/outputs/AI Inference Economics.xlsx
@@ -3779,7 +3779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4454,36 +4454,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Venice</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hyperscaler / big cloud</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>int4</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
         <v>0.03</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.4585392834237652</v>
+        <v>-0.6530111878802674</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.875123570054259</v>
+        <v>0.9918067127281603</v>
       </c>
     </row>
     <row r="18">
@@ -4494,36 +4494,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DekaLLM</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>hyperscaler / big cloud</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>bf16</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.03</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.377509323233556</v>
+        <v>-0.4585392834237652</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.8265055939401336</v>
+        <v>0.875123570054259</v>
       </c>
     </row>
     <row r="19">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>DekaLLM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4548,22 +4548,22 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.4585392834237652</v>
+        <v>-0.377509323233556</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.875123570054259</v>
+        <v>0.8265055939401336</v>
       </c>
     </row>
     <row r="20">
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0.187</v>
@@ -4614,36 +4614,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mancer 2</t>
+          <t>DeepInfra</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>major independent host</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>fp8</t>
+          <t>bf16</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.008193287271839655</v>
+        <v>-0.4585392834237652</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5950840276368962</v>
+        <v>0.875123570054259</v>
       </c>
     </row>
     <row r="22">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Novita</t>
+          <t>Mancer 2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>fp8</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -4734,36 +4734,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>Novita</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hyperscaler / big cloud</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.4096388614713331</v>
+        <v>0.008193287271839655</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.3542166831172001</v>
+        <v>0.5950840276368962</v>
       </c>
     </row>
     <row r="25">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DigitalOcean</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4788,22 +4788,22 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.311245338383222</v>
+        <v>0.4096388614713331</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.4132527969700668</v>
+        <v>0.3542166831172001</v>
       </c>
     </row>
     <row r="26">
@@ -4814,36 +4814,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BaseTen</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>hyperscaler / big cloud</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.5040966436359198</v>
+        <v>0.311245338383222</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.2975420138184481</v>
+        <v>0.4132527969700668</v>
       </c>
     </row>
     <row r="27">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Parasail</t>
+          <t>BaseTen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>major independent host</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4871,19 +4871,19 @@
         <v>0.1</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.6693977624239466</v>
+        <v>0.5040966436359198</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.1983613425456321</v>
+        <v>0.2975420138184481</v>
       </c>
     </row>
     <row r="28">
@@ -4894,36 +4894,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SambaNova</t>
+          <t>Parasail</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>custom chips</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.7389982334925893</v>
+        <v>0.6693977624239466</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.1566010599044464</v>
+        <v>0.1983613425456321</v>
       </c>
     </row>
     <row r="29">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amazon Bedrock</t>
+          <t>SambaNova</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>hyperscaler / big cloud</t>
+          <t>custom chips</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4948,22 +4948,22 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.5867472030299332</v>
+        <v>0.7389982334925893</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.2479516781820401</v>
+        <v>0.1566010599044464</v>
       </c>
     </row>
     <row r="30">
@@ -4974,17 +4974,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Amazon Bedrock</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>hyperscaler / big cloud</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>bf16</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -5054,17 +5054,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SiliconFlow</t>
+          <t>DeepInfra</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>major independent host</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>fp8</t>
+          <t>bf16</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Phala</t>
+          <t>SiliconFlow</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>fp8</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Together</t>
+          <t>Phala</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Groq</t>
+          <t>Together</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>custom chips</t>
+          <t>major independent host</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mara</t>
+          <t>Groq</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>custom chips</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5231,19 +5231,19 @@
         <v>0.15</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.6693977624239466</v>
+        <v>0.5867472030299332</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.1983613425456321</v>
+        <v>0.2479516781820401</v>
       </c>
     </row>
     <row r="37">
@@ -5254,21 +5254,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cerebras</t>
+          <t>Mara</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>custom chips</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>fp16</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0.75</v>
@@ -5283,6 +5283,46 @@
         <v>0.6693977624239466</v>
       </c>
       <c r="J37" s="6" t="n">
+        <v>0.1983613425456321</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cerebras</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>custom chips</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>fp16</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.2479516781820401</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>0.6693977624239466</v>
+      </c>
+      <c r="J38" s="6" t="n">
         <v>0.1983613425456321</v>
       </c>
     </row>
@@ -5694,22 +5734,22 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.425</v>
+        <v>0.25</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0.75</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2974702451508864</v>
+        <v>0.008193287271839655</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/AI Inference Economics.xlsx
+++ b/outputs/AI Inference Economics.xlsx
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Venice</t>
+          <t>Near AI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>int4</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -4494,36 +4494,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Venice</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hyperscaler / big cloud</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>int4</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.03</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.4585392834237652</v>
+        <v>-0.6530111878802674</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.875123570054259</v>
+        <v>0.9918067127281603</v>
       </c>
     </row>
     <row r="19">
@@ -4534,36 +4534,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DekaLLM</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>hyperscaler / big cloud</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>bf16</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.03</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.377509323233556</v>
+        <v>-0.4585392834237652</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.8265055939401336</v>
+        <v>0.875123570054259</v>
       </c>
     </row>
     <row r="20">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AkashML</t>
+          <t>DekaLLM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4591,19 +4591,19 @@
         <v>0.03</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.187</v>
+        <v>0.18</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.187</v>
+        <v>0.18</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.3259448031125138</v>
+        <v>-0.377509323233556</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.7955668818675082</v>
+        <v>0.8265055939401336</v>
       </c>
     </row>
     <row r="21">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>AkashML</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4628,22 +4628,22 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.17</v>
+        <v>0.187</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.17</v>
+        <v>0.187</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.4585392834237652</v>
+        <v>-0.3259448031125138</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.875123570054259</v>
+        <v>0.7955668818675082</v>
       </c>
     </row>
     <row r="22">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Crusoe</t>
+          <t>DeepInfra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>major independent host</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.008193287271839655</v>
+        <v>-0.4585392834237652</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.5950840276368962</v>
+        <v>0.875123570054259</v>
       </c>
     </row>
     <row r="23">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mancer 2</t>
+          <t>Crusoe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>fp8</t>
+          <t>bf16</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Novita</t>
+          <t>Mancer 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>fp8</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -4774,36 +4774,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>Novita</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hyperscaler / big cloud</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.4096388614713331</v>
+        <v>0.008193287271839655</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.3542166831172001</v>
+        <v>0.5950840276368962</v>
       </c>
     </row>
     <row r="26">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DigitalOcean</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4828,22 +4828,22 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.311245338383222</v>
+        <v>0.4096388614713331</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.4132527969700668</v>
+        <v>0.3542166831172001</v>
       </c>
     </row>
     <row r="27">
@@ -4854,36 +4854,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BaseTen</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>hyperscaler / big cloud</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.5040966436359198</v>
+        <v>0.311245338383222</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.2975420138184481</v>
+        <v>0.4132527969700668</v>
       </c>
     </row>
     <row r="28">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Parasail</t>
+          <t>BaseTen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>major independent host</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4911,19 +4911,19 @@
         <v>0.1</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.6693977624239466</v>
+        <v>0.5040966436359198</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.1983613425456321</v>
+        <v>0.2975420138184481</v>
       </c>
     </row>
     <row r="29">
@@ -4934,36 +4934,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SambaNova</t>
+          <t>Parasail</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>custom chips</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.7389982334925893</v>
+        <v>0.6693977624239466</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.1566010599044464</v>
+        <v>0.1983613425456321</v>
       </c>
     </row>
     <row r="30">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amazon Bedrock</t>
+          <t>SambaNova</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>hyperscaler / big cloud</t>
+          <t>custom chips</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4988,22 +4988,22 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.5867472030299332</v>
+        <v>0.7389982334925893</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.2479516781820401</v>
+        <v>0.1566010599044464</v>
       </c>
     </row>
     <row r="31">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Amazon Bedrock</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>hyperscaler / big cloud</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -5054,17 +5054,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>bf16</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0.17</v>
@@ -5716,7 +5716,7 @@
         <v>0.6</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.5454219233329265</v>
+        <v>0.5040966436359198</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>1</v>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.25</v>
@@ -5749,7 +5749,7 @@
         <v>0.008193287271839655</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/AI Inference Economics.xlsx
+++ b/outputs/AI Inference Economics.xlsx
@@ -4409,41 +4409,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llama 3.3 70B</t>
+          <t>gpt-oss-120b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Together</t>
+          <t>Near AI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.04</v>
+        <v>0.03</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.04</v>
+        <v>0.15</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.00208</v>
+        <v>0.15</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.000772885699196252</v>
+        <v>0.2479516781820401</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6284203369248789</v>
+        <v>-0.6530111878802674</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.2229477978450727</v>
+        <v>0.9918067127281603</v>
       </c>
     </row>
     <row r="17">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Near AI</t>
+          <t>Venice</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>int4</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -4494,36 +4494,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Venice</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>hyperscaler / big cloud</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>int4</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.03</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.6530111878802674</v>
+        <v>-0.4585392834237652</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.9918067127281603</v>
+        <v>0.875123570054259</v>
       </c>
     </row>
     <row r="19">
@@ -4534,36 +4534,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>DekaLLM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hyperscaler / big cloud</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>fp4</t>
+          <t>bf16</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.03</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.4585392834237652</v>
+        <v>-0.377509323233556</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.875123570054259</v>
+        <v>0.8265055939401336</v>
       </c>
     </row>
     <row r="20">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DekaLLM</t>
+          <t>AkashML</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4591,19 +4591,19 @@
         <v>0.03</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.18</v>
+        <v>0.187</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.18</v>
+        <v>0.187</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.377509323233556</v>
+        <v>-0.3259448031125138</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8265055939401336</v>
+        <v>0.7955668818675082</v>
       </c>
     </row>
     <row r="21">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AkashML</t>
+          <t>DeepInfra</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>long-tail independent host</t>
+          <t>major independent host</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4628,22 +4628,22 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.03</v>
+        <v>0.037</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.187</v>
+        <v>0.17</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.187</v>
+        <v>0.17</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.3259448031125138</v>
+        <v>-0.4585392834237652</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.7955668818675082</v>
+        <v>0.875123570054259</v>
       </c>
     </row>
     <row r="22">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>Crusoe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>major independent host</t>
+          <t>long-tail independent host</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.037</v>
+        <v>0.05</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.4585392834237652</v>
+        <v>0.008193287271839655</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.875123570054259</v>
+        <v>0.5950840276368962</v>
       </c>
     </row>
     <row r="23">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crusoe</t>
+          <t>Mancer 2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>bf16</t>
+          <t>fp8</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mancer 2</t>
+          <t>Novita</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>fp8</t>
+          <t>fp4</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Novita</t>
+          <t>Sail Research</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4788,22 +4788,22 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0.2479516781820401</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.008193287271839655</v>
+        <v>0.3801208045448998</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.5950840276368962</v>
+        <v>0.3719275172730601</v>
       </c>
     </row>
     <row r="26">
@@ -5584,19 +5584,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.68</v>
+        <v>0.32</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0.32</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.04</v>
+        <v>0.32</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.1058918543902414</v>
+        <v>-0.8402040457053617</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>1</v>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.25</v>
